--- a/data/trans_camb/IP04D$notiene-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$notiene-Habitat-trans_camb.xlsx
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,31; 17,55</t>
+          <t>6,86; 17,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 8,11</t>
+          <t>-0,59; 8,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,16; 21,0</t>
+          <t>8,28; 20,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 16,0</t>
+          <t>-2,6; 16,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,17; 17,48</t>
+          <t>9,06; 17,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 10,33</t>
+          <t>-0,19; 12,03</t>
         </is>
       </c>
     </row>
@@ -705,32 +705,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>129,13; 2467,45</t>
+          <t>130,16; 2245,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-19,01; 1067,02</t>
+          <t>-34,37; 1019,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>103,49; 821,79</t>
+          <t>102,79; 828,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-45,29; 606,1</t>
+          <t>-51,5; 565,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>155,65; 760,42</t>
+          <t>160,46; 808,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-16,32; 427,01</t>
+          <t>-15,59; 453,52</t>
         </is>
       </c>
     </row>
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,6; 13,86</t>
+          <t>5,38; 13,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,14; 20,64</t>
+          <t>6,55; 20,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,61; 16,15</t>
+          <t>7,78; 16,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,04; 12,6</t>
+          <t>4,37; 12,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,75; 13,79</t>
+          <t>7,86; 13,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,14; 14,04</t>
+          <t>6,23; 14,07</t>
         </is>
       </c>
     </row>
@@ -861,32 +861,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>97,88; 656,04</t>
+          <t>101,48; 720,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>113,12; 940,04</t>
+          <t>129,49; 989,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>153,49; 1037,53</t>
+          <t>155,78; 1047,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87,11; 872,94</t>
+          <t>88,66; 901,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>176,9; 660,97</t>
+          <t>172,16; 682,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>141,91; 658,23</t>
+          <t>139,33; 621,35</t>
         </is>
       </c>
     </row>
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,03; 14,81</t>
+          <t>3,52; 14,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,0; 21,86</t>
+          <t>5,17; 21,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,08; 21,7</t>
+          <t>10,09; 21,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,95; 26,75</t>
+          <t>13,26; 27,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,18; 17,09</t>
+          <t>8,56; 17,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,8; 22,09</t>
+          <t>10,42; 22,08</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1017,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39,71; 353,99</t>
+          <t>29,93; 315,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>59,55; 467,52</t>
+          <t>62,08; 461,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>129,28; 653,6</t>
+          <t>124,89; 639,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>158,54; 754,93</t>
+          <t>160,61; 797,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>122,45; 391,93</t>
+          <t>96,75; 363,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>154,69; 499,33</t>
+          <t>143,44; 482,16</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,82; 10,24</t>
+          <t>1,93; 10,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,95; 9,52</t>
+          <t>0,8; 9,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 7,72</t>
+          <t>-0,57; 7,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,42; 13,54</t>
+          <t>2,25; 13,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,11; 7,85</t>
+          <t>2,14; 7,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,96; 9,44</t>
+          <t>2,82; 9,72</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>24,14; 460,06</t>
+          <t>21,02; 457,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,83; 402,61</t>
+          <t>9,55; 401,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 328,93</t>
+          <t>-13,76; 315,22</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35,98; 617,02</t>
+          <t>33,85; 543,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>35,28; 273,52</t>
+          <t>36,06; 271,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>50,49; 321,34</t>
+          <t>48,04; 336,06</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,94; 11,42</t>
+          <t>6,86; 11,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,52; 13,17</t>
+          <t>6,66; 13,06</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,41; 13,77</t>
+          <t>8,7; 13,96</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,05; 13,23</t>
+          <t>6,92; 13,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,22; 11,79</t>
+          <t>8,29; 11,89</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,5; 12,07</t>
+          <t>7,46; 12,17</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1329,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>134,44; 351,49</t>
+          <t>131,52; 356,52</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>125,54; 385,4</t>
+          <t>133,5; 387,4</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>168,12; 436,14</t>
+          <t>168,1; 440,27</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>135,48; 402,23</t>
+          <t>135,43; 396,57</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>173,21; 339,98</t>
+          <t>167,17; 347,95</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>158,94; 348,7</t>
+          <t>157,66; 350,6</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$notiene-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$notiene-Habitat-trans_camb.xlsx
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,86; 17,73</t>
+          <t>6,93; 18,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 8,43</t>
+          <t>-0,3; 8,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,28; 20,41</t>
+          <t>6,95; 20,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 16,27</t>
+          <t>-2,51; 16,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,06; 17,6</t>
+          <t>9,08; 17,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 12,03</t>
+          <t>-0,25; 10,71</t>
         </is>
       </c>
     </row>
@@ -705,32 +705,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>130,16; 2245,97</t>
+          <t>115,57; 2343,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-34,37; 1019,3</t>
+          <t>-31,17; 1024,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>102,79; 828,93</t>
+          <t>81,0; 825,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-51,5; 565,23</t>
+          <t>-50,88; 538,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>160,46; 808,76</t>
+          <t>173,01; 764,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-15,59; 453,52</t>
+          <t>-18,1; 390,48</t>
         </is>
       </c>
     </row>
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,38; 13,71</t>
+          <t>5,59; 13,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,55; 20,61</t>
+          <t>6,59; 21,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,78; 16,16</t>
+          <t>7,73; 16,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,37; 12,47</t>
+          <t>4,39; 12,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,86; 13,78</t>
+          <t>7,72; 13,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,23; 14,07</t>
+          <t>6,18; 14,01</t>
         </is>
       </c>
     </row>
@@ -861,32 +861,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>101,48; 720,18</t>
+          <t>103,61; 694,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>129,49; 989,7</t>
+          <t>135,57; 1045,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>155,78; 1047,27</t>
+          <t>153,48; 1084,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>88,66; 901,97</t>
+          <t>88,42; 794,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>172,16; 682,46</t>
+          <t>191,59; 729,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>139,33; 621,35</t>
+          <t>145,09; 655,81</t>
         </is>
       </c>
     </row>
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,52; 14,67</t>
+          <t>3,83; 14,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,17; 21,82</t>
+          <t>5,07; 22,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,09; 21,64</t>
+          <t>10,13; 21,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,26; 27,69</t>
+          <t>13,27; 28,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,56; 17,0</t>
+          <t>8,94; 17,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,42; 22,08</t>
+          <t>11,14; 22,7</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1017,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29,93; 315,23</t>
+          <t>37,91; 331,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>62,08; 461,62</t>
+          <t>60,63; 474,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>124,89; 639,37</t>
+          <t>128,25; 622,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>160,61; 797,72</t>
+          <t>170,65; 796,85</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>96,75; 363,93</t>
+          <t>115,57; 374,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>143,44; 482,16</t>
+          <t>150,14; 493,53</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,93; 10,61</t>
+          <t>2,23; 10,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,8; 9,25</t>
+          <t>0,86; 9,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 7,34</t>
+          <t>-0,25; 7,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,25; 13,16</t>
+          <t>2,79; 13,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,14; 7,91</t>
+          <t>1,95; 7,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,82; 9,72</t>
+          <t>2,84; 9,41</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>21,02; 457,23</t>
+          <t>29,59; 453,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,55; 401,13</t>
+          <t>6,94; 387,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-13,76; 315,22</t>
+          <t>-8,86; 322,32</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33,85; 543,03</t>
+          <t>36,72; 578,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>36,06; 271,92</t>
+          <t>36,9; 313,4</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>48,04; 336,06</t>
+          <t>47,6; 330,83</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,86; 11,6</t>
+          <t>6,72; 11,38</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,66; 13,06</t>
+          <t>6,42; 13,11</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,7; 13,96</t>
+          <t>8,52; 13,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,92; 13,2</t>
+          <t>6,98; 12,95</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,29; 11,89</t>
+          <t>8,27; 11,91</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,46; 12,17</t>
+          <t>7,47; 12,09</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1329,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>131,52; 356,52</t>
+          <t>120,54; 348,25</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>133,5; 387,4</t>
+          <t>126,67; 386,93</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>168,1; 440,27</t>
+          <t>163,7; 410,62</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>135,43; 396,57</t>
+          <t>137,27; 390,23</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>167,17; 347,95</t>
+          <t>172,66; 347,91</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>157,66; 350,6</t>
+          <t>160,47; 351,65</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$notiene-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$notiene-Habitat-trans_camb.xlsx
@@ -511,19 +511,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que no dispone de calefacción en su vivienda</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -591,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14,29</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,03</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>12,09</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3,46</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>14,29</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,34</t>
+          <t>3,29</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -616,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,44</t>
+          <t>1,58</t>
         </is>
       </c>
     </row>
@@ -629,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,93; 18,03</t>
+          <t>8,16; 21,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 8,24</t>
+          <t>-4,6; 4,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,95; 20,63</t>
+          <t>6,31; 17,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 16,64</t>
+          <t>0,05; 7,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,08; 17,72</t>
+          <t>9,17; 17,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 10,71</t>
+          <t>-1,54; 4,73</t>
         </is>
       </c>
     </row>
@@ -667,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>296,84%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>538,32%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>153,91%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>296,84%</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>146,69%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -692,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>44,01%</t>
         </is>
       </c>
     </row>
@@ -705,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>115,57; 2343,54</t>
+          <t>103,49; 821,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-31,17; 1024,76</t>
+          <t>-66,75; 178,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81,0; 825,05</t>
+          <t>129,13; 2467,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-50,88; 538,19</t>
+          <t>-23,49; 1015,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>173,01; 764,19</t>
+          <t>155,65; 760,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,1; 390,48</t>
+          <t>-35,32; 216,93</t>
         </is>
       </c>
     </row>
@@ -747,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>11,74</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7,42</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>9,54</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>11,41</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>11,74</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,09</t>
+          <t>7,89</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -772,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,47</t>
+          <t>7,6</t>
         </is>
       </c>
     </row>
@@ -785,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,59; 13,7</t>
+          <t>7,61; 16,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,59; 21,86</t>
+          <t>3,6; 11,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,73; 16,17</t>
+          <t>5,6; 13,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,39; 12,45</t>
+          <t>3,98; 13,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,72; 13,68</t>
+          <t>7,75; 13,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,18; 14,01</t>
+          <t>4,77; 10,68</t>
         </is>
       </c>
     </row>
@@ -823,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>441,56%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>279,02%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>285,81%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>341,92%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>441,56%</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>304,1%</t>
+          <t>236,45%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -848,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>317,47%</t>
+          <t>254,66%</t>
         </is>
       </c>
     </row>
@@ -861,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>103,61; 694,21</t>
+          <t>153,49; 1037,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>135,57; 1045,57</t>
+          <t>78,67; 819,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>153,48; 1084,26</t>
+          <t>97,88; 656,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>88,42; 794,91</t>
+          <t>64,61; 604,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>191,59; 729,9</t>
+          <t>176,9; 660,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>145,09; 655,81</t>
+          <t>108,59; 529,21</t>
         </is>
       </c>
     </row>
@@ -903,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>16,11</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>17,77</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>9,43</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>14,35</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>16,11</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19,67</t>
+          <t>15,1</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -928,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,01</t>
+          <t>16,48</t>
         </is>
       </c>
     </row>
@@ -941,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,83; 14,66</t>
+          <t>10,08; 21,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,07; 22,36</t>
+          <t>11,68; 24,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,13; 21,54</t>
+          <t>4,03; 14,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,27; 28,11</t>
+          <t>9,12; 21,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,94; 17,39</t>
+          <t>9,18; 17,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,14; 22,7</t>
+          <t>11,8; 21,32</t>
         </is>
       </c>
     </row>
@@ -979,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>304,11%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>335,53%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>139,63%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>212,35%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>304,11%</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>371,4%</t>
+          <t>223,46%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1004,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>283,25%</t>
+          <t>274,46%</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37,91; 331,52</t>
+          <t>129,28; 653,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>60,63; 474,19</t>
+          <t>141,56; 694,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>128,25; 622,84</t>
+          <t>39,71; 353,99</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>170,65; 796,85</t>
+          <t>93,05; 474,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>115,57; 374,81</t>
+          <t>122,45; 391,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>150,14; 493,53</t>
+          <t>157,32; 467,86</t>
         </is>
       </c>
     </row>
@@ -1059,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3,51</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7,17</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>6,26</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>4,82</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3,51</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7,35</t>
+          <t>4,92</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1084,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,13</t>
+          <t>6,05</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,23; 10,41</t>
+          <t>-0,28; 7,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,86; 9,17</t>
+          <t>2,31; 13,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 7,19</t>
+          <t>1,82; 10,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,79; 13,45</t>
+          <t>0,95; 9,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,95; 7,85</t>
+          <t>2,11; 7,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,84; 9,41</t>
+          <t>2,92; 9,34</t>
         </is>
       </c>
     </row>
@@ -1135,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>87,37%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>178,33%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>154,82%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>119,02%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>87,37%</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>182,75%</t>
+          <t>121,7%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1160,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>151,89%</t>
+          <t>150,04%</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>29,59; 453,07</t>
+          <t>-8,03; 328,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,94; 387,19</t>
+          <t>31,54; 579,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 322,32</t>
+          <t>24,14; 460,06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36,72; 578,24</t>
+          <t>9,54; 410,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>36,9; 313,4</t>
+          <t>35,28; 273,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,6; 330,83</t>
+          <t>46,22; 318,67</t>
         </is>
       </c>
     </row>
@@ -1215,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>10,98</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>8,47</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>9,05</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>9,4</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>10,98</t>
-        </is>
-      </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9,82</t>
+          <t>8,1</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1240,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,63</t>
+          <t>8,3</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,72; 11,38</t>
+          <t>8,41; 13,77</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,42; 13,11</t>
+          <t>5,87; 11,25</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,52; 13,47</t>
+          <t>6,94; 11,42</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,98; 12,95</t>
+          <t>5,62; 10,69</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,27; 11,91</t>
+          <t>8,22; 11,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,47; 12,09</t>
+          <t>6,54; 10,27</t>
         </is>
       </c>
     </row>
@@ -1291,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>270,36%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>208,73%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>221,73%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>230,24%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>270,36%</t>
-        </is>
-      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>241,97%</t>
+          <t>198,43%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1316,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>236,44%</t>
+          <t>203,82%</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>120,54; 348,25</t>
+          <t>168,12; 436,14</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>126,67; 386,93</t>
+          <t>112,68; 347,46</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>163,7; 410,62</t>
+          <t>134,44; 351,49</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>137,27; 390,23</t>
+          <t>107,85; 332,32</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>172,66; 347,91</t>
+          <t>173,21; 339,98</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>160,47; 351,65</t>
+          <t>141,12; 298,9</t>
         </is>
       </c>
     </row>
